--- a/output/pdf_financials_xlsx/NCF.xlsx
+++ b/output/pdf_financials_xlsx/NCF.xlsx
@@ -5349,40 +5349,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.487902</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.36963</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.129361</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.577222</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.689356</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.009105</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.201269</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.285696</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.48461</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.586395</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.559293</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -8618,7 +8618,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10006,7 +10010,11 @@
           <t>Reserves 9 (c)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -10664,7 +10672,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -11882,7 +11894,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.487902</v>
       </c>

--- a/output/pdf_financials_xlsx/NCF.xlsx
+++ b/output/pdf_financials_xlsx/NCF.xlsx
@@ -971,40 +971,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.198434</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.217634</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07486</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08055900000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.030009</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006798</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.04245</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.061206</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.040486</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.010752</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.027292</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.179968</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1862,40 +1862,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.960465</v>
+        <v>-13.158899</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-14.24145</v>
+        <v>-14.459084</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-10.577021</v>
+        <v>-10.651881</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.997807</v>
+        <v>-4.078366</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.273586</v>
+        <v>-2.303595</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.460667</v>
+        <v>-1.467465</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.525552</v>
+        <v>-1.568002</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.462966</v>
+        <v>-1.524172</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.456999</v>
+        <v>-1.497485</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.306547</v>
+        <v>-1.317299</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.944483</v>
+        <v>-1.971775</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.77623</v>
+        <v>-2.956198</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -1968,40 +1968,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-12.960465</v>
+        <v>-13.158899</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-14.24145</v>
+        <v>-14.459084</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.577021</v>
+        <v>-10.651881</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.997807</v>
+        <v>-4.078366</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.273586</v>
+        <v>-2.303595</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.460667</v>
+        <v>-1.467465</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.525552</v>
+        <v>-1.568002</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.462966</v>
+        <v>-1.524172</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.456999</v>
+        <v>-1.497485</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.306547</v>
+        <v>-1.317299</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.944483</v>
+        <v>-1.971775</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.77623</v>
+        <v>-2.956198</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
@@ -27646,7 +27646,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">

--- a/output/pdf_financials_xlsx/NCF.xlsx
+++ b/output/pdf_financials_xlsx/NCF.xlsx
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.045311</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000976</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.045311</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000976</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-11.370105</v>
+        <v>-11.415416</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-11.685035</v>
+        <v>-11.686011</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-10.316635</v>
@@ -19112,7 +19112,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -20234,7 +20238,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>-0.045311</v>
       </c>
